--- a/Unity/Assets/Config/Excel/Datas/StartConfig/Localhost/StartMachineConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/StartConfig/Localhost/StartMachineConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\ET\Unity\Assets\Config\Excel\Datas\StartConfig\Localhost\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ChangeConfig\Benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D112FA0B-FD33-4EE2-ADF8-27075631F849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E046A1-E2C0-4B1E-A4DA-7E297A3189CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,33 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>InnerIP</t>
-  </si>
-  <si>
-    <t>OuterListenIP</t>
-  </si>
-  <si>
-    <t>OuterIP</t>
-  </si>
-  <si>
-    <t>WatcherPort</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>##</t>
@@ -57,7 +39,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>这是i</t>
@@ -67,7 +49,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>d</t>
@@ -75,25 +57,46 @@
   </si>
   <si>
     <t>内网地址</t>
-  </si>
-  <si>
-    <t>监听外网地址</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>InnerIP</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OuterIP</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>外网地址</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WatcherPort</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>守护进程端口</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>127.0.0.1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,19 +108,35 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -153,32 +172,25 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="差" xfId="1" builtinId="27"/>
+    <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="2" builtinId="26"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -451,113 +463,126 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
     <col min="2" max="2" width="15.875" customWidth="1"/>
-    <col min="3" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="15.25" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="22.375" customWidth="1"/>
-    <col min="8" max="8" width="16.875" customWidth="1"/>
-    <col min="9" max="9" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="12.375" customWidth="1"/>
+    <col min="5" max="5" width="12.125" customWidth="1"/>
+    <col min="6" max="6" width="22.375" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="5">
+        <v>13</v>
+      </c>
+      <c r="E4">
         <v>10000</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H11" s="6"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="G13" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
